--- a/artfynd/A 28013-2025 artfynd.xlsx
+++ b/artfynd/A 28013-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>125960253</v>
       </c>
       <c r="B3" t="n">
-        <v>91697</v>
+        <v>91698</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>125960197</v>
       </c>
       <c r="B4" t="n">
-        <v>91697</v>
+        <v>91698</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28013-2025 artfynd.xlsx
+++ b/artfynd/A 28013-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>125960253</v>
       </c>
       <c r="B3" t="n">
-        <v>91698</v>
+        <v>91701</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>125960197</v>
       </c>
       <c r="B4" t="n">
-        <v>91698</v>
+        <v>91701</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28013-2025 artfynd.xlsx
+++ b/artfynd/A 28013-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>125960253</v>
       </c>
       <c r="B3" t="n">
-        <v>91701</v>
+        <v>91705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>125960197</v>
       </c>
       <c r="B4" t="n">
-        <v>91701</v>
+        <v>91705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28013-2025 artfynd.xlsx
+++ b/artfynd/A 28013-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125960370</v>
       </c>
       <c r="B2" t="n">
-        <v>43933</v>
+        <v>43934</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>125960253</v>
       </c>
       <c r="B3" t="n">
-        <v>91705</v>
+        <v>91707</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>125960197</v>
       </c>
       <c r="B4" t="n">
-        <v>91705</v>
+        <v>91707</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28013-2025 artfynd.xlsx
+++ b/artfynd/A 28013-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>125960253</v>
       </c>
       <c r="B3" t="n">
-        <v>91707</v>
+        <v>91709</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>125960197</v>
       </c>
       <c r="B4" t="n">
-        <v>91707</v>
+        <v>91709</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28013-2025 artfynd.xlsx
+++ b/artfynd/A 28013-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>125960253</v>
       </c>
       <c r="B3" t="n">
-        <v>91709</v>
+        <v>91711</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>125960197</v>
       </c>
       <c r="B4" t="n">
-        <v>91709</v>
+        <v>91711</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28013-2025 artfynd.xlsx
+++ b/artfynd/A 28013-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>125960253</v>
       </c>
       <c r="B3" t="n">
-        <v>91711</v>
+        <v>91715</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>125960197</v>
       </c>
       <c r="B4" t="n">
-        <v>91711</v>
+        <v>91715</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28013-2025 artfynd.xlsx
+++ b/artfynd/A 28013-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125960370</v>
       </c>
       <c r="B2" t="n">
-        <v>43934</v>
+        <v>43935</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>125960253</v>
       </c>
       <c r="B3" t="n">
-        <v>91715</v>
+        <v>91718</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>125960197</v>
       </c>
       <c r="B4" t="n">
-        <v>91715</v>
+        <v>91718</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28013-2025 artfynd.xlsx
+++ b/artfynd/A 28013-2025 artfynd.xlsx
@@ -1055,7 +1055,7 @@
         <v>127039232</v>
       </c>
       <c r="B5" t="n">
-        <v>92727</v>
+        <v>92802</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>127038953</v>
       </c>
       <c r="B7" t="n">
-        <v>91298</v>
+        <v>91372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>127038737</v>
       </c>
       <c r="B8" t="n">
-        <v>91718</v>
+        <v>91792</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>127039071</v>
       </c>
       <c r="B9" t="n">
-        <v>91874</v>
+        <v>91948</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 28013-2025 artfynd.xlsx
+++ b/artfynd/A 28013-2025 artfynd.xlsx
@@ -1055,7 +1055,7 @@
         <v>127039232</v>
       </c>
       <c r="B5" t="n">
-        <v>92802</v>
+        <v>92808</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>127038953</v>
       </c>
       <c r="B7" t="n">
-        <v>91372</v>
+        <v>91378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>127038737</v>
       </c>
       <c r="B8" t="n">
-        <v>91792</v>
+        <v>91798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>127039071</v>
       </c>
       <c r="B9" t="n">
-        <v>91948</v>
+        <v>91954</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 28013-2025 artfynd.xlsx
+++ b/artfynd/A 28013-2025 artfynd.xlsx
@@ -1055,7 +1055,7 @@
         <v>127039232</v>
       </c>
       <c r="B5" t="n">
-        <v>92808</v>
+        <v>92809</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>127038953</v>
       </c>
       <c r="B7" t="n">
-        <v>91378</v>
+        <v>91379</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>127038737</v>
       </c>
       <c r="B8" t="n">
-        <v>91798</v>
+        <v>91799</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>127039071</v>
       </c>
       <c r="B9" t="n">
-        <v>91954</v>
+        <v>91955</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 28013-2025 artfynd.xlsx
+++ b/artfynd/A 28013-2025 artfynd.xlsx
@@ -1055,7 +1055,7 @@
         <v>127039232</v>
       </c>
       <c r="B5" t="n">
-        <v>92809</v>
+        <v>92813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>127038483</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>127038953</v>
       </c>
       <c r="B7" t="n">
-        <v>91379</v>
+        <v>91383</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>127038737</v>
       </c>
       <c r="B8" t="n">
-        <v>91799</v>
+        <v>91803</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>127039071</v>
       </c>
       <c r="B9" t="n">
-        <v>91955</v>
+        <v>91959</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>127151209</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28013-2025 artfynd.xlsx
+++ b/artfynd/A 28013-2025 artfynd.xlsx
@@ -1055,7 +1055,7 @@
         <v>127039232</v>
       </c>
       <c r="B5" t="n">
-        <v>92813</v>
+        <v>92815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>127038953</v>
       </c>
       <c r="B7" t="n">
-        <v>91383</v>
+        <v>91385</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>127038737</v>
       </c>
       <c r="B8" t="n">
-        <v>91803</v>
+        <v>91805</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>127039071</v>
       </c>
       <c r="B9" t="n">
-        <v>91959</v>
+        <v>91961</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>127151209</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28013-2025 artfynd.xlsx
+++ b/artfynd/A 28013-2025 artfynd.xlsx
@@ -1055,7 +1055,7 @@
         <v>127039232</v>
       </c>
       <c r="B5" t="n">
-        <v>92815</v>
+        <v>92821</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>127038953</v>
       </c>
       <c r="B7" t="n">
-        <v>91385</v>
+        <v>91391</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>127038737</v>
       </c>
       <c r="B8" t="n">
-        <v>91805</v>
+        <v>91811</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>127039071</v>
       </c>
       <c r="B9" t="n">
-        <v>91961</v>
+        <v>91967</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 28013-2025 artfynd.xlsx
+++ b/artfynd/A 28013-2025 artfynd.xlsx
@@ -1678,7 +1678,7 @@
         <v>127151209</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28013-2025 artfynd.xlsx
+++ b/artfynd/A 28013-2025 artfynd.xlsx
@@ -1678,7 +1678,7 @@
         <v>127151209</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28013-2025 artfynd.xlsx
+++ b/artfynd/A 28013-2025 artfynd.xlsx
@@ -1055,7 +1055,7 @@
         <v>127039232</v>
       </c>
       <c r="B5" t="n">
-        <v>92821</v>
+        <v>92802</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>127038483</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>8447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>127038953</v>
       </c>
       <c r="B7" t="n">
-        <v>91391</v>
+        <v>91372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>127038737</v>
       </c>
       <c r="B8" t="n">
-        <v>91811</v>
+        <v>91792</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>127039071</v>
       </c>
       <c r="B9" t="n">
-        <v>91967</v>
+        <v>91948</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>127151209</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28013-2025 artfynd.xlsx
+++ b/artfynd/A 28013-2025 artfynd.xlsx
@@ -1055,7 +1055,7 @@
         <v>127039232</v>
       </c>
       <c r="B5" t="n">
-        <v>92802</v>
+        <v>92821</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>127038483</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>127038953</v>
       </c>
       <c r="B7" t="n">
-        <v>91372</v>
+        <v>91391</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>127038737</v>
       </c>
       <c r="B8" t="n">
-        <v>91792</v>
+        <v>91811</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>127039071</v>
       </c>
       <c r="B9" t="n">
-        <v>91948</v>
+        <v>91967</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>127151209</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28013-2025 artfynd.xlsx
+++ b/artfynd/A 28013-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125960370</v>
+        <v>127039071</v>
       </c>
       <c r="B2" t="n">
-        <v>43935</v>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,32 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101735</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +721,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>318554</v>
+        <v>318665</v>
       </c>
       <c r="R2" t="n">
-        <v>6545060</v>
+        <v>6544962</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,22 +771,22 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog m löv</t>
+          <t>Fuktig granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Fnöskticka på björkstubbe. # Fomes fomentarius</t>
+          <t>Låga # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125960253</v>
+        <v>127039232</v>
       </c>
       <c r="B3" t="n">
-        <v>91718</v>
+        <v>91962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +815,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5467</v>
+        <v>2079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>318597</v>
+        <v>318676</v>
       </c>
       <c r="R3" t="n">
-        <v>6544967</v>
+        <v>6544995</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -874,12 +876,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,7 +896,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Fuktig barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -927,40 +929,36 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125960197</v>
+        <v>127038953</v>
       </c>
       <c r="B4" t="n">
-        <v>91718</v>
+        <v>91966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5467</v>
+        <v>5321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -969,13 +967,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>318612</v>
+        <v>318626</v>
       </c>
       <c r="R4" t="n">
-        <v>6544922</v>
+        <v>6545024</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,12 +997,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,22 +1017,22 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1052,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127039232</v>
+        <v>125960197</v>
       </c>
       <c r="B5" t="n">
-        <v>92821</v>
+        <v>92398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,21 +1061,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>5467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1094,10 +1092,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>318676</v>
+        <v>318612</v>
       </c>
       <c r="R5" t="n">
-        <v>6544995</v>
+        <v>6544922</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1124,12 +1122,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,7 +1142,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Fuktig barrskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1177,43 +1175,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127038483</v>
+        <v>125960253</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>92398</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>5467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1221,10 +1217,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>318578</v>
+        <v>318597</v>
       </c>
       <c r="R6" t="n">
-        <v>6544960</v>
+        <v>6544967</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1251,12 +1247,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,7 +1267,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Bärljungblandskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1286,7 +1282,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Gadd # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1304,32 +1300,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127038953</v>
+        <v>127038737</v>
       </c>
       <c r="B7" t="n">
-        <v>91391</v>
+        <v>92398</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5321</v>
+        <v>5467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1342,10 +1338,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>318626</v>
+        <v>318625</v>
       </c>
       <c r="R7" t="n">
-        <v>6545024</v>
+        <v>6544985</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -1392,22 +1388,22 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1425,10 +1421,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127038737</v>
+        <v>127151209</v>
       </c>
       <c r="B8" t="n">
-        <v>91811</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,26 +1432,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5467</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1463,13 +1464,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>318625</v>
+        <v>318570</v>
       </c>
       <c r="R8" t="n">
-        <v>6544985</v>
+        <v>6545061</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1501,35 +1502,19 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldtre spår efter födosökande.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1546,10 +1531,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127039071</v>
+        <v>125960370</v>
       </c>
       <c r="B9" t="n">
-        <v>91967</v>
+        <v>44177</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,34 +1542,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1339</v>
+        <v>101735</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1592,13 +1575,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>318665</v>
+        <v>318554</v>
       </c>
       <c r="R9" t="n">
-        <v>6544962</v>
+        <v>6545060</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1622,12 +1605,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1642,22 +1625,22 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Fuktig granskog</t>
+          <t>Bärljungbarrskog m löv</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Låga # Picea abies</t>
+          <t>Fnöskticka på björkstubbe. # Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1675,40 +1658,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127151209</v>
+        <v>127038483</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>8455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1718,10 +1702,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>318570</v>
+        <v>318578</v>
       </c>
       <c r="R10" t="n">
-        <v>6545061</v>
+        <v>6544960</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1756,19 +1740,35 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldtre spår efter födosökande.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Bärljungblandskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Gadd # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">

--- a/artfynd/A 28013-2025 artfynd.xlsx
+++ b/artfynd/A 28013-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -801,6 +806,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127039071</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -926,6 +936,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127039232</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,6 +1062,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127038953</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1172,6 +1192,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125960197</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1297,6 +1322,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125960253</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1418,6 +1448,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127038737</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1528,6 +1563,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127151209</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1655,6 +1695,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125960370</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1782,8 +1827,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127038483</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>